--- a/Checklist/Checklist Biometria v29072025.xlsx
+++ b/Checklist/Checklist Biometria v29072025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mberrutto\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mberrutto\Documents\GitHub\PentestResources\Checklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5441E3F1-A324-42D6-A95B-425861217BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2BCC75-1762-4468-B268-539715BF40AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Descripción</t>
   </si>
@@ -60,45 +60,15 @@
     <t>Prueba</t>
   </si>
   <si>
-    <t>Utilizar un Documento Nacional de Identidad (DNI) generado digitalmente mediante edición o software de creación gráfica, para evaluar si el sistema puede ser engañado con documentos no emitidos oficialmente.</t>
-  </si>
-  <si>
-    <t>Foto de Redes Sociales</t>
-  </si>
-  <si>
-    <t>Usar una imagen obtenida de redes sociales del titular, en alta calidad y resolución, para comprobar si una simple imagen digital puede ser utilizada para suplantación de identidad.</t>
-  </si>
-  <si>
-    <t>Foto impresa o en pantalla de redes</t>
-  </si>
-  <si>
-    <t>Presentar una foto del rostro impresa en papel o reproducida en un monitor para determinar si el sistema detecta la falta de profundidad o textura real.</t>
-  </si>
-  <si>
-    <t>Video de redes sociales</t>
-  </si>
-  <si>
-    <t>Utilizar un video legítimo del titular extraído de redes sociales, donde se presenten gestos y movimientos faciales, con el fin de probar si la biometría reconoce patrones de movimiento falsos como válidos.</t>
-  </si>
-  <si>
     <t>Video generado por IA</t>
   </si>
   <si>
-    <t>Crear un video artificial a partir de una imagen del titular utilizando herramientas de generación por inteligencia artificial (ej.: D-ID, DeepFaceLab) para simular una presentación válida.</t>
-  </si>
-  <si>
     <t>Realizar la validación en condiciones de poca luz, con sombras o iluminación directa, para verificar si estas afectan la precisión del reconocimiento facial.</t>
   </si>
   <si>
     <t>Cubrir partes del rostro con elementos como barbijos, anteojos oscuros, gorros o bufandas, para evaluar la tolerancia del sistema a obstrucciones faciales.</t>
   </si>
   <si>
-    <t>Distancia o ángulo atípico</t>
-  </si>
-  <si>
-    <t>Posicionar el rostro de manera no frontal, demasiado cerca o lejos de la cámara, para comprobar si el sistema exige condiciones específicas de encuadre.</t>
-  </si>
-  <si>
     <t>Interceptar la imagen capturada durante el proceso de validación y reemplazarla por una imagen predefinida, analizando si existe verificación de origen o integridad.</t>
   </si>
   <si>
@@ -108,24 +78,9 @@
     <t>Introducir intencionalmente demoras o variaciones en la calidad de la conexión durante la validación para detectar si el sistema se ve afectado por problemas de red.</t>
   </si>
   <si>
-    <t>Reemplazar la entrada de la cámara en tiempo real utilizando herramientas como OBS Virtual Camera o v4l2loopback, con el objetivo de validar si la aplicación distingue entre cámaras físicas y virtuales.</t>
-  </si>
-  <si>
-    <t>Foto de DNI Digital</t>
-  </si>
-  <si>
     <t>DNI Digital Falso</t>
   </si>
   <si>
-    <t>Presentar una imagen fotográfica real de un DNI legítimo, en formato digital, con el objetivo de verificar si el sistema acepta documentos reales pero no presenciales como sustituto de la validación facial.</t>
-  </si>
-  <si>
-    <t>Inyección de imagen en flujo HTTP</t>
-  </si>
-  <si>
-    <t>Reemplazar la imagen interceptado el request HTTP  utilizando herramientas como Burp.</t>
-  </si>
-  <si>
     <t>Resultado</t>
   </si>
   <si>
@@ -136,13 +91,34 @@
   </si>
   <si>
     <t>https://github.com/CyberSecurityUP/Facial-Recognition-PenTest-Checklist</t>
+  </si>
+  <si>
+    <t>Utilizar un Documento Nacional de Identidad (DNI) generado digitalmente mediante edición o software de creación gráfica o IA, para evaluar si el sistema puede ser engañado con documentos no emitidos oficialmente.</t>
+  </si>
+  <si>
+    <t>Foto de DNI legítimo.</t>
+  </si>
+  <si>
+    <t>Presentar una imagen fotográfica real de un DNI legítimo, en formato digital, con el objetivo de verificar si el sistema acepta documentos reales, pero no presenciales como sustituto de la validación.</t>
+  </si>
+  <si>
+    <t>Fotos y Videos de Redes Sociales</t>
+  </si>
+  <si>
+    <t>Usar una imagen y video obtenida de redes sociales del titular, en alta calidad y resolución, para comprobar si pueden ser utilizadas para suplantación de identidad.</t>
+  </si>
+  <si>
+    <t>Crear un video artificial a partir de una imagen del titular utilizando herramientas de generación por inteligencia artificial para simular una presentación válida.</t>
+  </si>
+  <si>
+    <t>Reemplazar la entrada de la cámara en tiempo real utilizando herramientas como OBS Virtual Camera, con el objetivo de validar si la aplicación distingue entre cámaras físicas y virtuales.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +142,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -181,7 +163,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -205,14 +187,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -224,14 +215,8 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -244,6 +229,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -525,187 +516,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.109375" customWidth="1"/>
     <col min="3" max="3" width="77.21875" customWidth="1"/>
     <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+      <c r="C5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="5"/>
+      <c r="D10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -715,18 +659,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>30</v>
+      <c r="A1" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>31</v>
+      <c r="A2" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>32</v>
+      <c r="A3" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
